--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.36.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.36.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.36.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.36.xlsx
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="39" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.36.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.36.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0036.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0036.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -595,18 +595,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œamended " before the word bill.â€� For such New</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]29</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]29</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L7: isolated marker/symbol line :: 29</t>
@@ -614,7 +614,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]29</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -641,7 +641,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -653,7 +653,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: s :â€” %</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -661,7 +661,7 @@
       <c r="N3" s="1" t="inlineStr"/>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L18: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -700,7 +700,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 1</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -747,7 +747,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -755,7 +755,7 @@
       <c r="N5" s="1" t="inlineStr"/>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: *</t>
+          <t>L35: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -798,7 +798,7 @@
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: r.)</t>
+          <t>L38: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -841,7 +841,7 @@
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L57: symbol-only separator/garbage line :: 1030</t>
+          <t>L54: isolated marker/symbol line :: r.)</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -884,7 +884,7 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L57: symbol-only separator/garbage line :: 1030</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -927,7 +927,7 @@
       <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: \</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -970,7 +970,7 @@
       <c r="N10" s="1" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L61: isolated marker/symbol line :: \</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       <c r="N11" s="1" t="inlineStr"/>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: A.</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       <c r="N12" s="1" t="inlineStr"/>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: t</t>
+          <t>L65: isolated marker/symbol line :: A.</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1097,7 +1097,11 @@
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr"/>
-      <c r="O13" s="1" t="inlineStr"/>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>L67: isolated marker/symbol line :: t</t>
+        </is>
+      </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr"/>
